--- a/config/generated/templates/Ability.xlsx
+++ b/config/generated/templates/Ability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
   <si>
     <t>@table</t>
   </si>
@@ -43,7 +43,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>84664aadc17d2fc8</t>
+    <t>e585469aa7aa7a4a</t>
   </si>
   <si>
     <t>#name</t>
@@ -64,6 +64,9 @@
     <t>cooldown_actions</t>
   </si>
   <si>
+    <t>semantic_tags_mask</t>
+  </si>
+  <si>
     <t>entry_rule_identity_id</t>
   </si>
   <si>
@@ -104,6 +107,9 @@
   </si>
   <si>
     <t>range=0..100</t>
+  </si>
+  <si>
+    <t>range=0..2047</t>
   </si>
   <si>
     <t>#desc</t>
@@ -533,7 +539,8 @@
     <col min="5" max="5" width="20.7109375" style="5" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" style="5" customWidth="1"/>
     <col min="7" max="7" width="16.7109375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="32.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -593,10 +600,13 @@
       <c r="H2" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="I2" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -618,37 +628,43 @@
       </c>
       <c r="H3" s="5" t="s">
         <v>16</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>24</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -669,30 +685,36 @@
         <v>7</v>
       </c>
       <c r="H5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -701,9 +723,10 @@
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Basic, Skill, Ultimate, Talent, Technique, EnhancedBasic, EnhancedSkill, FollowUp, Counter, Summon, Memosprite, Passive, Entry" promptTitle="AbilityKind enum" prompt="Select a value from the dropdown." sqref="C8:C1007">
       <formula1>"Basic,Skill,Ultimate,Talent,Technique,EnhancedBasic,EnhancedSkill,FollowUp,Counter,Summon,Memosprite,Passive,Entry"</formula1>
     </dataValidation>
@@ -721,6 +744,10 @@
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 2047." promptTitle="Integer range" prompt="Enter an integer from 0 to 2047." sqref="H8:H1007">
+      <formula1>0</formula1>
+      <formula2>2047</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/generated/templates/Ability.xlsx
+++ b/config/generated/templates/Ability.xlsx
@@ -727,8 +727,8 @@
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Basic, Skill, Ultimate, Talent, Technique, EnhancedBasic, EnhancedSkill, FollowUp, Counter, Summon, Memosprite, Passive, Entry" promptTitle="AbilityKind enum" prompt="Select a value from the dropdown." sqref="C8:C1007">
-      <formula1>"Basic,Skill,Ultimate,Talent,Technique,EnhancedBasic,EnhancedSkill,FollowUp,Counter,Summon,Memosprite,Passive,Entry"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Basic, Skill, Ultimate, Talent, Technique, EnhancedBasic, EnhancedSkill, FollowUp, Counter, Summon, Memosprite, Passive, Entry, Countdown" promptTitle="AbilityKind enum" prompt="Select a value from the dropdown." sqref="C8:C1007">
+      <formula1>"Basic,Skill,Ultimate,Talent,Technique,EnhancedBasic,EnhancedSkill,FollowUp,Counter,Summon,Memosprite,Passive,Entry,Countdown"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: SingleTarget, Blast, Aoe, Bounce, Support, Enhance, None, ContentDefined" promptTitle="TargetPattern enum" prompt="Select a value from the dropdown." sqref="D8:D1007">
       <formula1>"SingleTarget,Blast,Aoe,Bounce,Support,Enhance,None,ContentDefined"</formula1>

--- a/config/generated/templates/Ability.xlsx
+++ b/config/generated/templates/Ability.xlsx
@@ -43,7 +43,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>e585469aa7aa7a4a</t>
+    <t>8bed349bb757ef1d</t>
   </si>
   <si>
     <t>#name</t>
@@ -109,7 +109,7 @@
     <t>range=0..100</t>
   </si>
   <si>
-    <t>range=0..2047</t>
+    <t>range=0..4095</t>
   </si>
   <si>
     <t>#desc</t>
@@ -744,9 +744,9 @@
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 2047." promptTitle="Integer range" prompt="Enter an integer from 0 to 2047." sqref="H8:H1007">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 4095." promptTitle="Integer range" prompt="Enter an integer from 0 to 4095." sqref="H8:H1007">
       <formula1>0</formula1>
-      <formula2>2047</formula2>
+      <formula2>4095</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/generated/templates/Ability.xlsx
+++ b/config/generated/templates/Ability.xlsx
@@ -34,16 +34,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>8bed349bb757ef1d</t>
+    <t>36ad0e4ca629a421</t>
   </si>
   <si>
     <t>#name</t>
@@ -94,7 +94,7 @@
     <t>optional&lt;ref&lt;ContentIdentity.id&gt;&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
